--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2021_tarapaca.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 21:45</t>
+    <t xml:space="preserve">2026-08-17 12:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2021_tarapaca.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 12:35</t>
+    <t xml:space="preserve">2026-08-28 11:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2021_tarapaca.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:32</t>
+    <t xml:space="preserve">2026-09-07 11:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
